--- a/outputs/37554.xlsx
+++ b/outputs/37554.xlsx
@@ -335,124 +335,128 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="4" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="4" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="7" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="7" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="4" borderId="7" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="4" borderId="7" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="9" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="9" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="10" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="4" borderId="9" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="10" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="4" borderId="9" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="13" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -709,380 +713,380 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="36.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4" t="str">
+      <c r="C1" s="4"/>
+      <c r="D1" s="5" t="str">
         <f aca="false">A1</f>
         <v>TYPE</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="str">
+      <c r="F1" s="6" t="str">
         <f aca="false">B1</f>
         <v>Accounts</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="8" t="n">
         <v>4377</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="11" t="n">
         <f aca="false">IFERROR(F2/$F$18,"")</f>
         <v>0.00969220694171578</v>
       </c>
-      <c r="F2" s="11" t="n">
-        <f aca="false">IF(D2="","",SUMPRODUCT((D2=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F2" s="12" t="n">
+        <f aca="false">IF(D2="","",SUMIF($A$2:$A$17,D2,$B$2:$B$17))</f>
         <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="14" t="n">
         <v>1629</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="16" t="n">
         <f aca="false">IFERROR(F3/$F$18,"")</f>
         <v>0.000523903077930583</v>
       </c>
-      <c r="F3" s="16" t="n">
-        <f aca="false">IF(D3="","",SUMPRODUCT((D3=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F3" s="17" t="n">
+        <f aca="false">IF(D3="","",SUMIF($A$2:$A$17,D3,$B$2:$B$17))</f>
         <v>4</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="14" t="n">
         <v>824</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="14" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <f aca="false">IFERROR(F4/$F$18,"")</f>
         <v>0.57328094302554</v>
       </c>
-      <c r="F4" s="16" t="n">
-        <f aca="false">IF(D4="","",SUMPRODUCT((D4=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F4" s="17" t="n">
+        <f aca="false">IF(D4="","",SUMIF($A$2:$A$17,D4,$B$2:$B$17))</f>
         <v>4377</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="14" t="n">
         <v>181</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <f aca="false">IFERROR(F5/$F$18,"")</f>
         <v>0.00537000654878847</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <f aca="false">IF(D5="","",SUMPRODUCT((D5=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F5" s="17" t="n">
+        <f aca="false">IF(D5="","",SUMIF($A$2:$A$17,D5,$B$2:$B$17))</f>
         <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <v>176</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="14" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="16" t="n">
         <f aca="false">IFERROR(F6/$F$18,"")</f>
         <v>0.000130975769482646</v>
       </c>
-      <c r="F6" s="16" t="n">
-        <f aca="false">IF(D6="","",SUMPRODUCT((D6=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F6" s="17" t="n">
+        <f aca="false">IF(D6="","",SUMIF($A$2:$A$17,D6,$B$2:$B$17))</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>122</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="14" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="16" t="n">
         <f aca="false">IFERROR(F7/$F$18,"")</f>
         <v>0.00275049115913556</v>
       </c>
-      <c r="F7" s="16" t="n">
-        <f aca="false">IF(D7="","",SUMPRODUCT((D7=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F7" s="17" t="n">
+        <f aca="false">IF(D7="","",SUMIF($A$2:$A$17,D7,$B$2:$B$17))</f>
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>117</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="14" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="16" t="n">
         <f aca="false">IFERROR(F8/$F$18,"")</f>
         <v>0.0014407334643091</v>
       </c>
-      <c r="F8" s="16" t="n">
-        <f aca="false">IF(D8="","",SUMPRODUCT((D8=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F8" s="17" t="n">
+        <f aca="false">IF(D8="","",SUMIF($A$2:$A$17,D8,$B$2:$B$17))</f>
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="16" t="n">
         <f aca="false">IFERROR(F9/$F$18,"")</f>
         <v>0.21335952848723</v>
       </c>
-      <c r="F9" s="16" t="n">
-        <f aca="false">IF(D9="","",SUMPRODUCT((D9=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F9" s="17" t="n">
+        <f aca="false">IF(D9="","",SUMIF($A$2:$A$17,D9,$B$2:$B$17))</f>
         <v>1629</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="14" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="16" t="n">
         <f aca="false">IFERROR(F10/$F$18,"")</f>
         <v>0.0159790438768828</v>
       </c>
-      <c r="F10" s="16" t="n">
-        <f aca="false">IF(D10="","",SUMPRODUCT((D10=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F10" s="17" t="n">
+        <f aca="false">IF(D10="","",SUMIF($A$2:$A$17,D10,$B$2:$B$17))</f>
         <v>122</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="9"/>
+      <c r="D11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="16" t="n">
         <f aca="false">IFERROR(F11/$F$18,"")</f>
         <v>0.0153241650294695</v>
       </c>
-      <c r="F11" s="16" t="n">
-        <f aca="false">IF(D11="","",SUMPRODUCT((D11=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F11" s="17" t="n">
+        <f aca="false">IF(D11="","",SUMIF($A$2:$A$17,D11,$B$2:$B$17))</f>
         <v>117</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="14" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="16" t="n">
         <f aca="false">IFERROR(F12/$F$18,"")</f>
         <v>0.0237066142763589</v>
       </c>
-      <c r="F12" s="16" t="n">
-        <f aca="false">IF(D12="","",SUMPRODUCT((D12=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F12" s="17" t="n">
+        <f aca="false">IF(D12="","",SUMIF($A$2:$A$17,D12,$B$2:$B$17))</f>
         <v>181</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="14" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="16" t="n">
         <f aca="false">IFERROR(F13/$F$18,"")</f>
         <v>0.0230517354289456</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <f aca="false">IF(D13="","",SUMPRODUCT((D13=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F13" s="17" t="n">
+        <f aca="false">IF(D13="","",SUMIF($A$2:$A$17,D13,$B$2:$B$17))</f>
         <v>176</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="14" t="s">
+      <c r="C14" s="9"/>
+      <c r="D14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="16" t="n">
         <f aca="false">IFERROR(F14/$F$18,"")</f>
         <v>0.000261951538965291</v>
       </c>
-      <c r="F14" s="16" t="n">
-        <f aca="false">IF(D14="","",SUMPRODUCT((D14=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F14" s="17" t="n">
+        <f aca="false">IF(D14="","",SUMIF($A$2:$A$17,D14,$B$2:$B$17))</f>
         <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="16" t="n">
         <f aca="false">IFERROR(F15/$F$18,"")</f>
         <v>0.00222658808120498</v>
       </c>
-      <c r="F15" s="16" t="n">
-        <f aca="false">IF(D15="","",SUMPRODUCT((D15=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F15" s="17" t="n">
+        <f aca="false">IF(D15="","",SUMIF($A$2:$A$17,D15,$B$2:$B$17))</f>
         <v>17</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="14" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="16" t="n">
         <f aca="false">IFERROR(F16/$F$18,"")</f>
         <v>0.1079240340537</v>
       </c>
-      <c r="F16" s="16" t="n">
-        <f aca="false">IF(D16="","",SUMPRODUCT((D16=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F16" s="17" t="n">
+        <f aca="false">IF(D16="","",SUMIF($A$2:$A$17,D16,$B$2:$B$17))</f>
         <v>824</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="20" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="22" t="n">
         <f aca="false">IFERROR(F17/$F$18,"")</f>
         <v>0.00497707924034054</v>
       </c>
-      <c r="F17" s="22" t="n">
-        <f aca="false">IF(D17="","",SUMPRODUCT((D17=$A$2:$A$17)*$B$2:$B$17))</f>
+      <c r="F17" s="23" t="n">
+        <f aca="false">IF(D17="","",SUMIF($A$2:$A$17,D17,$B$2:$B$17))</f>
         <v>38</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24" t="n">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25" t="n">
         <f aca="false">SUM(B2:B17)</f>
         <v>7635</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="25" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="27" t="n">
         <f aca="false">SUM(E2:E17)</f>
         <v>1</v>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="28" t="n">
         <f aca="false">SUM(F2:F17)</f>
         <v>7635</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="28" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="30" t="n">
         <f aca="false">F18-B18</f>
         <v>0</v>
       </c>

--- a/outputs/37554.xlsx
+++ b/outputs/37554.xlsx
@@ -748,13 +748,13 @@
       <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="11" t="str">
         <f aca="false">IFERROR(F2/$F$18,"")</f>
-        <v>0.00969220694171578</v>
+        <v/>
       </c>
       <c r="F2" s="12" t="n">
-        <f aca="false">IF(D2="","",SUMIF($A$2:$A$17,D2,$B$2:$B$17))</f>
-        <v>74</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A2)*(ISNUMBER(SEARCH($D2,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -768,13 +768,13 @@
       <c r="D3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="16" t="str">
         <f aca="false">IFERROR(F3/$F$18,"")</f>
-        <v>0.000523903077930583</v>
+        <v/>
       </c>
       <c r="F3" s="17" t="n">
-        <f aca="false">IF(D3="","",SUMIF($A$2:$A$17,D3,$B$2:$B$17))</f>
-        <v>4</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A3)*(ISNUMBER(SEARCH($D3,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
@@ -790,13 +790,13 @@
       <c r="D4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="16" t="str">
         <f aca="false">IFERROR(F4/$F$18,"")</f>
-        <v>0.57328094302554</v>
+        <v/>
       </c>
       <c r="F4" s="17" t="n">
-        <f aca="false">IF(D4="","",SUMIF($A$2:$A$17,D4,$B$2:$B$17))</f>
-        <v>4377</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A4)*(ISNUMBER(SEARCH($D4,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -810,13 +810,13 @@
       <c r="D5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="16" t="str">
         <f aca="false">IFERROR(F5/$F$18,"")</f>
-        <v>0.00537000654878847</v>
+        <v/>
       </c>
       <c r="F5" s="17" t="n">
-        <f aca="false">IF(D5="","",SUMIF($A$2:$A$17,D5,$B$2:$B$17))</f>
-        <v>41</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A5)*(ISNUMBER(SEARCH($D5,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -830,13 +830,13 @@
       <c r="D6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="16" t="str">
         <f aca="false">IFERROR(F6/$F$18,"")</f>
-        <v>0.000130975769482646</v>
+        <v/>
       </c>
       <c r="F6" s="17" t="n">
-        <f aca="false">IF(D6="","",SUMIF($A$2:$A$17,D6,$B$2:$B$17))</f>
-        <v>1</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A6)*(ISNUMBER(SEARCH($D6,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -850,13 +850,13 @@
       <c r="D7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="16" t="str">
         <f aca="false">IFERROR(F7/$F$18,"")</f>
-        <v>0.00275049115913556</v>
+        <v/>
       </c>
       <c r="F7" s="17" t="n">
-        <f aca="false">IF(D7="","",SUMIF($A$2:$A$17,D7,$B$2:$B$17))</f>
-        <v>21</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A7)*(ISNUMBER(SEARCH($D7,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -870,13 +870,13 @@
       <c r="D8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="16" t="str">
         <f aca="false">IFERROR(F8/$F$18,"")</f>
-        <v>0.0014407334643091</v>
+        <v/>
       </c>
       <c r="F8" s="17" t="n">
-        <f aca="false">IF(D8="","",SUMIF($A$2:$A$17,D8,$B$2:$B$17))</f>
-        <v>11</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A8)*(ISNUMBER(SEARCH($D8,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -890,13 +890,13 @@
       <c r="D9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="16" t="str">
         <f aca="false">IFERROR(F9/$F$18,"")</f>
-        <v>0.21335952848723</v>
+        <v/>
       </c>
       <c r="F9" s="17" t="n">
-        <f aca="false">IF(D9="","",SUMIF($A$2:$A$17,D9,$B$2:$B$17))</f>
-        <v>1629</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A9)*(ISNUMBER(SEARCH($D9,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -910,13 +910,13 @@
       <c r="D10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="16" t="str">
         <f aca="false">IFERROR(F10/$F$18,"")</f>
-        <v>0.0159790438768828</v>
+        <v/>
       </c>
       <c r="F10" s="17" t="n">
-        <f aca="false">IF(D10="","",SUMIF($A$2:$A$17,D10,$B$2:$B$17))</f>
-        <v>122</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A10)*(ISNUMBER(SEARCH($D10,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -930,13 +930,13 @@
       <c r="D11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="16" t="str">
         <f aca="false">IFERROR(F11/$F$18,"")</f>
-        <v>0.0153241650294695</v>
+        <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <f aca="false">IF(D11="","",SUMIF($A$2:$A$17,D11,$B$2:$B$17))</f>
-        <v>117</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A11)*(ISNUMBER(SEARCH($D11,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -950,13 +950,13 @@
       <c r="D12" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="16" t="str">
         <f aca="false">IFERROR(F12/$F$18,"")</f>
-        <v>0.0237066142763589</v>
+        <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <f aca="false">IF(D12="","",SUMIF($A$2:$A$17,D12,$B$2:$B$17))</f>
-        <v>181</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A12)*(ISNUMBER(SEARCH($D12,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -970,13 +970,13 @@
       <c r="D13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="16" t="str">
         <f aca="false">IFERROR(F13/$F$18,"")</f>
-        <v>0.0230517354289456</v>
+        <v/>
       </c>
       <c r="F13" s="17" t="n">
-        <f aca="false">IF(D13="","",SUMIF($A$2:$A$17,D13,$B$2:$B$17))</f>
-        <v>176</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A13)*(ISNUMBER(SEARCH($D13,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -990,13 +990,13 @@
       <c r="D14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="16" t="str">
         <f aca="false">IFERROR(F14/$F$18,"")</f>
-        <v>0.000261951538965291</v>
+        <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <f aca="false">IF(D14="","",SUMIF($A$2:$A$17,D14,$B$2:$B$17))</f>
-        <v>2</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A14)*(ISNUMBER(SEARCH($D14,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1010,13 +1010,13 @@
       <c r="D15" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="16" t="str">
         <f aca="false">IFERROR(F15/$F$18,"")</f>
-        <v>0.00222658808120498</v>
+        <v/>
       </c>
       <c r="F15" s="17" t="n">
-        <f aca="false">IF(D15="","",SUMIF($A$2:$A$17,D15,$B$2:$B$17))</f>
-        <v>17</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A15)*(ISNUMBER(SEARCH($D15,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1030,13 +1030,13 @@
       <c r="D16" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="16" t="str">
         <f aca="false">IFERROR(F16/$F$18,"")</f>
-        <v>0.1079240340537</v>
+        <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <f aca="false">IF(D16="","",SUMIF($A$2:$A$17,D16,$B$2:$B$17))</f>
-        <v>824</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A16)*(ISNUMBER(SEARCH($D16,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1050,13 +1050,13 @@
       <c r="D17" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="22" t="str">
         <f aca="false">IFERROR(F17/$F$18,"")</f>
-        <v>0.00497707924034054</v>
+        <v/>
       </c>
       <c r="F17" s="23" t="n">
-        <f aca="false">IF(D17="","",SUMIF($A$2:$A$17,D17,$B$2:$B$17))</f>
-        <v>38</v>
+        <f aca="false">SUMPRODUCT(($A$2:$A$17=A17)*(ISNUMBER(SEARCH($D17,$A$2:$A$17))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="E18" s="27" t="n">
         <f aca="false">SUM(E2:E17)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="28" t="n">
         <f aca="false">SUM(F2:F17)</f>
-        <v>7635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F19" s="30" t="n">
         <f aca="false">F18-B18</f>
-        <v>0</v>
+        <v>-7635</v>
       </c>
     </row>
   </sheetData>
